--- a/saidas/metricas_resumo/qtd/4_b_top_5/parte_1_historico_completo.xlsx
+++ b/saidas/metricas_resumo/qtd/4_b_top_5/parte_1_historico_completo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Modelo</t>
   </si>
@@ -46,61 +46,37 @@
     <t>&lt; 50%</t>
   </si>
   <si>
+    <t>SARIMA</t>
+  </si>
+  <si>
     <t>SE(LINE)+SE(SGDR)+ABR</t>
   </si>
   <si>
-    <t>SPct+ABR</t>
-  </si>
-  <si>
-    <t>SARIMA</t>
-  </si>
-  <si>
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
-    <t>SE(ABR)+MAS+OHE+ABR</t>
-  </si>
-  <si>
-    <t>SE(ETR)+MMS+BIN+SE(ELAS)+ABR</t>
-  </si>
-  <si>
-    <t>88/211</t>
-  </si>
-  <si>
-    <t>85/211</t>
-  </si>
-  <si>
-    <t>98/211</t>
-  </si>
-  <si>
-    <t>87/211</t>
-  </si>
-  <si>
-    <t>96/211</t>
-  </si>
-  <si>
-    <t>158/211</t>
-  </si>
-  <si>
-    <t>154/211</t>
-  </si>
-  <si>
-    <t>160/211</t>
-  </si>
-  <si>
-    <t>152/211</t>
-  </si>
-  <si>
-    <t>156/211</t>
-  </si>
-  <si>
-    <t>144/211</t>
-  </si>
-  <si>
-    <t>211/211</t>
-  </si>
-  <si>
-    <t>210/211</t>
+    <t>116/262</t>
+  </si>
+  <si>
+    <t>107/262</t>
+  </si>
+  <si>
+    <t>108/262</t>
+  </si>
+  <si>
+    <t>188/262</t>
+  </si>
+  <si>
+    <t>191/262</t>
+  </si>
+  <si>
+    <t>186/262</t>
+  </si>
+  <si>
+    <t>261/262</t>
+  </si>
+  <si>
+    <t>262/262</t>
   </si>
 </sst>
 </file>
@@ -458,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -498,31 +474,31 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>7.41</v>
+        <v>7.62</v>
       </c>
       <c r="C2">
-        <v>9.49</v>
+        <v>10.13</v>
       </c>
       <c r="D2">
-        <v>0.345</v>
+        <v>0.362</v>
       </c>
       <c r="E2">
-        <v>59.6</v>
+        <v>13.6</v>
       </c>
       <c r="F2">
-        <v>264.9</v>
+        <v>277.9</v>
       </c>
       <c r="G2">
-        <v>31.26</v>
+        <v>50.83</v>
       </c>
       <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -530,31 +506,31 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>7.47</v>
+        <v>7.63</v>
       </c>
       <c r="C3">
-        <v>9.59</v>
+        <v>9.84</v>
       </c>
       <c r="D3">
-        <v>0.336</v>
+        <v>0.399</v>
       </c>
       <c r="E3">
-        <v>61</v>
+        <v>37.7</v>
       </c>
       <c r="F3">
-        <v>266.6</v>
+        <v>267.3</v>
       </c>
       <c r="G3">
-        <v>31.26</v>
+        <v>31.45</v>
       </c>
       <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -562,127 +538,31 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>7.16</v>
+        <v>8.01</v>
       </c>
       <c r="C4">
-        <v>9.609999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="D4">
-        <v>0.345</v>
+        <v>0.365</v>
       </c>
       <c r="E4">
-        <v>23.9</v>
+        <v>22.2</v>
       </c>
       <c r="F4">
-        <v>270.6</v>
+        <v>276.8</v>
       </c>
       <c r="G4">
-        <v>52.1</v>
+        <v>35.74</v>
       </c>
       <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
         <v>18</v>
       </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
       <c r="J4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>7.89</v>
-      </c>
-      <c r="C5">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="D5">
-        <v>0.313</v>
-      </c>
-      <c r="E5">
-        <v>40.5</v>
-      </c>
-      <c r="F5">
-        <v>275.2</v>
-      </c>
-      <c r="G5">
-        <v>34.06</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>7.32</v>
-      </c>
-      <c r="C6">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="D6">
-        <v>0.328</v>
-      </c>
-      <c r="E6">
-        <v>43.7</v>
-      </c>
-      <c r="F6">
-        <v>271.6</v>
-      </c>
-      <c r="G6">
-        <v>34.42</v>
-      </c>
-      <c r="H6" t="s">
         <v>20</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>7.67</v>
-      </c>
-      <c r="C7">
-        <v>9.73</v>
-      </c>
-      <c r="D7">
-        <v>0.311</v>
-      </c>
-      <c r="E7">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="F7">
-        <v>269.6</v>
-      </c>
-      <c r="G7">
-        <v>29.6</v>
-      </c>
-      <c r="H7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
